--- a/event_registration_forms/027_junior_showmanship_entry_form--event_registration_forms.xlsx
+++ b/event_registration_forms/027_junior_showmanship_entry_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -777,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>competition_info_form</t>
+          <t>competition_info_form_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Competition Info</t>
+          <t>Competition Info Form 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Competition Entries</t>
+          <t>Competition Entries Form</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Entries</t>
+          <t>Entries Form</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Division</t>
+          <t>Division Form Select</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Select all divisions</t>
+          <t>Division Form Select All Select</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select one division</t>
+          <t>Division Form Select One Select</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Select one division</t>
+          <t>Division Form Select All Select One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Select multiple divisions</t>
+          <t>Division Form Select Multiple Select Select</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Select one or more divisions</t>
+          <t>Division Form Select Multiple 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Junior Handler</t>
+          <t>Handler Form Handler</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>division_form</t>
+          <t>division_form_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Division</t>
+          <t>Division Form 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>competition_form</t>
+          <t>competition_form_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>Competition Form 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>entries_form</t>
+          <t>entries_form_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Entries</t>
+          <t>Entries Form 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>division_form_select</t>
+          <t>division_form_select_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Select one or more divisions</t>
+          <t>Division Form Select 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>division_form_select_choices</t>
+          <t>division_form_select_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>division_form_select_choices</t>
+          <t>division_form_select_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
